--- a/Result/profitability/2923.xlsx
+++ b/Result/profitability/2923.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8177,6 +8177,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2205</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1073</v>
+      </c>
+      <c r="F62" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-492</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-22.34%</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>624</v>
+      </c>
+      <c r="J62" t="n">
+        <v>132</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-225</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-0.4275</v>
+      </c>
+      <c r="N62" t="n">
+        <v>52.21125</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W62" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X62" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-10.48</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-0.1771467207572683</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>-0.7045454545454546</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.7857666911225238</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
